--- a/01_INPUTS/INNOVACIONES/Innovaciones.xlsx
+++ b/01_INPUTS/INNOVACIONES/Innovaciones.xlsx
@@ -1,194 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\INNOVACIONES\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278AA0BA-7095-4924-80C5-1A9FA3BD9419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="innovaciones" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="innovaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
-  <si>
-    <t>AASS c/plan</t>
-  </si>
-  <si>
-    <t>74813 - DADA EXTRA BRUT 6X750</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>80094 - NC SPARK EXTRA BRUT LATA 4X6X355</t>
-  </si>
-  <si>
-    <t>14619 - FRIZZE BUBBLE MOOD 6X1000</t>
-  </si>
-  <si>
-    <t>74830 - DADA SIDRA 6X750</t>
-  </si>
-  <si>
-    <t>30139 - GORDON'S TROPICAL FRUITS 6x700</t>
-  </si>
-  <si>
-    <t>74749 - INTOCABLES DOUBLE OAK 6x750</t>
-  </si>
-  <si>
-    <t>44396 - BLEND DE EXTREMOS PN PN 6X750</t>
-  </si>
-  <si>
-    <t>14578 - TERMIDOR TRAD B-D SLIM 12X1L</t>
-  </si>
-  <si>
-    <t>42376 - DON DAVID RED BLEND 6X750</t>
-  </si>
-  <si>
-    <t>74814 - CAZADOR MALBEC 6X750</t>
-  </si>
-  <si>
-    <t>74815 - CAZADOR CAB. SAU 6X750</t>
-  </si>
-  <si>
-    <t>74816 - CAZADOR BLANCO DULCE 6X750</t>
-  </si>
-  <si>
-    <t>74827 - ALMA MORA BLANCO DULCE LOW    6X750</t>
-  </si>
-  <si>
-    <t>74840 - TRAPICHE DULCE COSECHA TINTO 6X750</t>
-  </si>
-  <si>
-    <t>74786 - EL BAUTISMO CABERNET 6X750</t>
-  </si>
-  <si>
-    <t>60020 -Antares XPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14620 - Frizze Manxana Pop </t>
-  </si>
-  <si>
-    <t>60021 - Antares Porron 330</t>
-  </si>
-  <si>
-    <t>60022 - Antares Porron 660</t>
-  </si>
-  <si>
-    <t>74884 - Dada lata tinto verano</t>
-  </si>
-  <si>
-    <t>42377 - Don David Torrontes Low 6x750</t>
-  </si>
-  <si>
-    <t>74882 - Los Arboles bco dulce 6x750</t>
-  </si>
-  <si>
-    <t>90105 - Cinz. VTH RSO 12X1000</t>
-  </si>
-  <si>
-    <t>90106 - Cinz. VTH BI AM 12X1000</t>
-  </si>
-  <si>
-    <t>90110 - Cinz. VTH SEGUNDO 6X750</t>
-  </si>
-  <si>
-    <t>74886 - Dada sweet red Low 6x750</t>
-  </si>
-  <si>
-    <t>74883 - Dada sweet white Low 6x750</t>
-  </si>
-  <si>
-    <t>EL ULTIMO TRAMO MALBEC 6X750</t>
-  </si>
-  <si>
-    <t>EL ULTIMO TRAMO CABERNET SAUVI 6X750</t>
-  </si>
-  <si>
-    <t>EL ULTIMO TRAMO TORRON NARANJ 6X750</t>
-  </si>
-  <si>
-    <t>FRIZZE MAN-GO PARTY 6X1000</t>
-  </si>
-  <si>
-    <t>EDMUNDO MALBEC 6X750</t>
-  </si>
-  <si>
-    <t>EDMUNDO CABERNET 6X750</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
+        <bgColor theme="4" tint="0.7999816888943144"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,7 +95,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </bottom>
       <diagonal/>
     </border>
@@ -241,19 +115,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -323,14 +197,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -650,292 +584,446 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="5" customWidth="1"/>
+    <col width="46.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.42578125" customWidth="1" style="5" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C1" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+    <row r="1">
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>AASS c/plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>74813 - DADA EXTRA BRUT 6X750</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>80094 - NC SPARK EXTRA BRUT LATA 4X6X355</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>14619 - FRIZZE BUBBLE MOOD 6X1000</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>74830 - DADA SIDRA 6X750</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>30139 - GORDON'S TROPICAL FRUITS 6x700</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>74749 - INTOCABLES DOUBLE OAK 6x750</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>44396 - BLEND DE EXTREMOS PN PN 6X750</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>14578 - TERMIDOR TRAD B-D SLIM 12X1L</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>42376 - DON DAVID RED BLEND 6X750</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>74814 - CAZADOR MALBEC 6X750</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>74815 - CAZADOR CAB. SAU 6X750</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>74816 - CAZADOR BLANCO DULCE 6X750</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>74827 - ALMA MORA BLANCO DULCE LOW    6X750</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>74840 - TRAPICHE DULCE COSECHA TINTO 6X750</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>74786 - EL BAUTISMO CABERNET 6X750</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>60020 -Antares XPA</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14620 - Frizze Manxana Pop </t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>60021 - Antares Porron 330</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>60022 - Antares Porron 660</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>74884 - Dada lata tinto verano</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>42377 - Don David Torrontes Low 6x750</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>74882 - Los Arboles bco dulce 6x750</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>90105 - Cinz. VTH RSO 12X1000</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>90106 - Cinz. VTH BI AM 12X1000</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>90110 - Cinz. VTH SEGUNDO 6X750</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>74886 - Dada sweet red Low 6x750</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>74883 - Dada sweet white Low 6x750</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
         <v>74901</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>EL ULTIMO TRAMO MALBEC 6X750</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
         <v>74902</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>EL ULTIMO TRAMO CABERNET SAUVI 6X750</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
         <v>74903</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>EL ULTIMO TRAMO TORRON NARANJ 6X750</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
         <v>14621</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>FRIZZE MAN-GO PARTY 6X1000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
         <v>74909</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>EDMUNDO MALBEC 6X750</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
         <v>74910</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>34</v>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>EDMUNDO CABERNET 6X750</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A29:A31">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" priority="5" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="6" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:A34">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
